--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MICHIGAN_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MICHIGAN_2018.xlsx
@@ -535,7 +535,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="15">
@@ -2191,7 +2191,7 @@
         <v>5</v>
       </c>
       <c r="D102">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="103">
@@ -2371,7 +2371,7 @@
         <v>5</v>
       </c>
       <c r="D112">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="113">
@@ -2965,7 +2965,7 @@
         <v>5</v>
       </c>
       <c r="D145">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="146">
@@ -3217,7 +3217,7 @@
         <v>5</v>
       </c>
       <c r="D159">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="160">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C202">
@@ -4135,7 +4135,7 @@
         <v>5</v>
       </c>
       <c r="D210">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="211">
@@ -4513,7 +4513,7 @@
         <v>5</v>
       </c>
       <c r="D231">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="232">
@@ -4603,7 +4603,7 @@
         <v>5</v>
       </c>
       <c r="D236">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="237">
@@ -4657,7 +4657,7 @@
         <v>5</v>
       </c>
       <c r="D239">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="240">
@@ -4927,7 +4927,7 @@
         <v>5</v>
       </c>
       <c r="D254">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="255">
@@ -5017,7 +5017,7 @@
         <v>5</v>
       </c>
       <c r="D259">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="260">
@@ -6277,7 +6277,7 @@
         <v>5</v>
       </c>
       <c r="D329">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="330">
@@ -6547,7 +6547,7 @@
         <v>5</v>
       </c>
       <c r="D344">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="345">
@@ -6583,7 +6583,7 @@
         <v>5</v>
       </c>
       <c r="D346">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="347">
@@ -6817,7 +6817,7 @@
         <v>5</v>
       </c>
       <c r="D359">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="360">
@@ -8617,7 +8617,7 @@
         <v>5</v>
       </c>
       <c r="D459">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="460">
@@ -9085,7 +9085,7 @@
         <v>5</v>
       </c>
       <c r="D485">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="486">
@@ -9121,7 +9121,7 @@
         <v>5</v>
       </c>
       <c r="D487">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="488">
@@ -9319,7 +9319,7 @@
         <v>5</v>
       </c>
       <c r="D498">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="499">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C507">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C508">
@@ -9697,7 +9697,7 @@
         <v>5</v>
       </c>
       <c r="D519">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="520">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C558">
@@ -11497,7 +11497,7 @@
         <v>5</v>
       </c>
       <c r="D619">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="620">
@@ -12253,7 +12253,7 @@
         <v>5</v>
       </c>
       <c r="D661">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="662">
@@ -12595,7 +12595,7 @@
         <v>5</v>
       </c>
       <c r="D680">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="681">
@@ -13963,7 +13963,7 @@
         <v>5</v>
       </c>
       <c r="D756">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="757">
@@ -14197,7 +14197,7 @@
         <v>5</v>
       </c>
       <c r="D769">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="770">
@@ -15655,7 +15655,7 @@
         <v>5</v>
       </c>
       <c r="D850">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="851">
@@ -16321,7 +16321,7 @@
         <v>5</v>
       </c>
       <c r="D887">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="888">
@@ -16897,7 +16897,7 @@
         <v>5</v>
       </c>
       <c r="D919">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="920">
@@ -17203,7 +17203,7 @@
         <v>5</v>
       </c>
       <c r="D936">
-        <v>0.0009416195856873823</v>
+        <v>0.0009416195856873824</v>
       </c>
     </row>
     <row r="937">
